--- a/test/kevin-test.xlsx
+++ b/test/kevin-test.xlsx
@@ -31,7 +31,7 @@
   <etc:cellImage>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="ID_03E3D9CC3CAD4D80BC52CFAD9FA841D9"/>
+        <xdr:cNvPr id="17" name="ID_43CB9C70A73E4C3C80385D7854AFA313"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -44,8 +44,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2847340" y="279400"/>
-          <a:ext cx="4200525" cy="6391275"/>
+          <a:off x="4761865" y="3784600"/>
+          <a:ext cx="4248150" cy="7515225"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -60,7 +60,7 @@
   <etc:cellImage>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="ID_B9F901458AAC4119951AC509CAA849C9"/>
+        <xdr:cNvPr id="15" name="ID_D6D0FC3305F44C7FB61802EAE81D71DB"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -73,8 +73,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4761865" y="1155700"/>
-          <a:ext cx="4419600" cy="8610600"/>
+          <a:off x="4761865" y="2032000"/>
+          <a:ext cx="4381500" cy="7162800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -89,7 +89,7 @@
   <etc:cellImage>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="ID_6D4054353E034C5995655C0F0F8CE46E"/>
+        <xdr:cNvPr id="14" name="ID_FE51128C7808427FAE3DB40A613386FE"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -102,8 +102,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4761865" y="2032000"/>
-          <a:ext cx="4133850" cy="7905750"/>
+          <a:off x="4761865" y="1155700"/>
+          <a:ext cx="3971925" cy="6362700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -118,7 +118,7 @@
   <etc:cellImage>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="ID_498DCE23504243D582817C15DF221162"/>
+        <xdr:cNvPr id="16" name="ID_F2475BDC7B71434AAF47DCEFCA0B3D43"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -131,8 +131,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8074660" y="2032000"/>
-          <a:ext cx="4705350" cy="6410325"/>
+          <a:off x="4761865" y="2908300"/>
+          <a:ext cx="3971925" cy="7448550"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -147,7 +147,7 @@
   <etc:cellImage>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="ID_448E5FC704D94C2A9E5B627A79EE967B"/>
+        <xdr:cNvPr id="13" name="ID_5FE0ED88047D478A9F42F972027B315A"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -160,95 +160,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4761865" y="2908300"/>
-          <a:ext cx="4314825" cy="8201025"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="ID_63399EC3E80B4566A60D0ECFCBDE3B4C"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4761865" y="3784600"/>
-          <a:ext cx="4705350" cy="8515350"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="ID_064B3120738647D99CDB63B6CE8AF18D"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4761865" y="4660900"/>
-          <a:ext cx="4162425" cy="7829550"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="ID_4941D6FE75C14F29B42CCFDE86C8F2E8"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4761865" y="5537200"/>
-          <a:ext cx="10306050" cy="6677025"/>
+          <a:off x="4761865" y="279400"/>
+          <a:ext cx="4181475" cy="7267575"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -264,7 +177,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>路径</t>
   </si>
@@ -281,56 +194,34 @@
     <t>处理状态</t>
   </si>
   <si>
-    <t>拼豆-我的预约</t>
+    <t>mp-底部tab</t>
   </si>
   <si>
-    <t>1. 页面列表样式要调整，卡片最好横铺，取消预约应该在卡片内部</t>
+    <t>底部tab的样式不对</t>
   </si>
   <si>
-    <t>拼豆-绑定微信信息</t>
+    <t>mp-选择门店</t>
   </si>
   <si>
-    <t xml:space="preserve">1. 页面应该都显示中文（其他页面也检查一下）；
-2. 绑定手机号失败
-3. 绑定信息后，应立刻支付，才能预约，而不是先生成二维码，再支付
-</t>
+    <t>点击选择门店时，弹出的列表应该是悬浮的，如果不好做，就做成底部弹框吧；目前的向下推压的效果不好</t>
   </si>
   <si>
-    <t>回收</t>
+    <t>mp-拼豆</t>
   </si>
   <si>
-    <t>1. 物品有分类，还应该有ip，比如火影，比如海贼王之类的，用户可以输入也可以选择；
-2. 预估金额的功能，暂时不要
-3. 应该有一个预估时长的功能
-4. 这种录入环节放在底部弹框会不会更好，回收板块更多做显示
-5. 我觉得到店不应该是一个时间段，而应该是一个确定的时间点，给门店提醒，超时30分钟预约自动失效</t>
+    <t>样式和间距调整一下：1. 标题和上面的间距；2. 到店须知的内间距；3. 选时段一排三个</t>
   </si>
   <si>
-    <t>我的-预约看板</t>
+    <t>mp-回收</t>
   </si>
   <si>
-    <t>1. 整体设计很乱，调整一下</t>
+    <t>页面样式调整：1. 通知的内边距；2. 标题的间距；3. 填写回收物品后的内边距；4. 预计回收时间用户不用操作，我觉得放在编辑回收物品里一起显示；5. 如果当天的选择到店时间已经有人约了，则要变灰</t>
   </si>
   <si>
-    <t>我的-谷子号外</t>
+    <t>mp-我的</t>
   </si>
   <si>
-    <t>1. 卡片应该横向平铺，宽度应保持一致</t>
-  </si>
-  <si>
-    <t>admin-菜单</t>
-  </si>
-  <si>
-    <t>1. 一级菜单添加icon；二级菜单不要icon
-2. 一级菜单应该和模块相关：主要有：系统管理，通用配置，拼豆业务，回收业务，扭蛋，预购。按模块分，而不是所有内容都放在谷子业务里</t>
-  </si>
-  <si>
-    <t>admin-券模版</t>
-  </si>
-  <si>
-    <t>1. 折扣类型下拉没数据；
-2. 适用业务不要显示拼音
-3. 发放策略应该有地方配置，比如新人，比如特定时间注册的人，比如执行过拼豆的人之类的</t>
+    <t>1. 不需要收藏；2. 我的订单，我的图鉴都去掉，我开过的叫做扭蛋记录；3. 样式调整一下，现在卡片内都没有边距，</t>
   </si>
 </sst>
 </file>
@@ -959,13 +850,16 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -973,9 +867,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1503,119 +1397,91 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="69" customHeight="1" outlineLevelRow="7" outlineLevelCol="4"/>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="69" customHeight="1" outlineLevelRow="5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="18.875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="39.7109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="40.7578125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="22.3984375" style="2" customWidth="1"/>
-    <col min="5" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="18.875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="39.7109375" style="4" customWidth="1"/>
+    <col min="3" max="3" width="40.7578125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="22.3984375" style="3" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="22" customHeight="1" spans="1:5">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="1:3">
+    <row r="2" s="2" customFormat="1" customHeight="1" spans="1:3">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="2" t="str">
-        <f>_xlfn.DISPIMG("ID_03E3D9CC3CAD4D80BC52CFAD9FA841D9",1)</f>
-        <v>=DISPIMG("ID_03E3D9CC3CAD4D80BC52CFAD9FA841D9",1)</v>
+        <f>_xlfn.DISPIMG("ID_5FE0ED88047D478A9F42F972027B315A",1)</f>
+        <v>=DISPIMG("ID_5FE0ED88047D478A9F42F972027B315A",1)</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="1:3">
+    <row r="3" s="2" customFormat="1" customHeight="1" spans="1:3">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C3" s="2" t="str">
-        <f>_xlfn.DISPIMG("ID_B9F901458AAC4119951AC509CAA849C9",1)</f>
-        <v>=DISPIMG("ID_B9F901458AAC4119951AC509CAA849C9",1)</v>
+        <f>_xlfn.DISPIMG("ID_FE51128C7808427FAE3DB40A613386FE",1)</f>
+        <v>=DISPIMG("ID_FE51128C7808427FAE3DB40A613386FE",1)</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:4">
+    <row r="4" s="2" customFormat="1" customHeight="1" spans="1:3">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C4" s="2" t="str">
-        <f>_xlfn.DISPIMG("ID_6D4054353E034C5995655C0F0F8CE46E",1)</f>
-        <v>=DISPIMG("ID_6D4054353E034C5995655C0F0F8CE46E",1)</v>
-      </c>
-      <c r="D4" s="2" t="str">
-        <f>_xlfn.DISPIMG("ID_498DCE23504243D582817C15DF221162",1)</f>
-        <v>=DISPIMG("ID_498DCE23504243D582817C15DF221162",1)</v>
+        <f>_xlfn.DISPIMG("ID_D6D0FC3305F44C7FB61802EAE81D71DB",1)</f>
+        <v>=DISPIMG("ID_D6D0FC3305F44C7FB61802EAE81D71DB",1)</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:3">
+    <row r="5" s="2" customFormat="1" customHeight="1" spans="1:3">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="2" t="str">
-        <f>_xlfn.DISPIMG("ID_448E5FC704D94C2A9E5B627A79EE967B",1)</f>
-        <v>=DISPIMG("ID_448E5FC704D94C2A9E5B627A79EE967B",1)</v>
+        <f>_xlfn.DISPIMG("ID_F2475BDC7B71434AAF47DCEFCA0B3D43",1)</f>
+        <v>=DISPIMG("ID_F2475BDC7B71434AAF47DCEFCA0B3D43",1)</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:3">
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="1:3">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C6" s="2" t="str">
-        <f>_xlfn.DISPIMG("ID_63399EC3E80B4566A60D0ECFCBDE3B4C",1)</f>
-        <v>=DISPIMG("ID_63399EC3E80B4566A60D0ECFCBDE3B4C",1)</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="1:3">
-      <c r="A7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="2" t="str">
-        <f>_xlfn.DISPIMG("ID_064B3120738647D99CDB63B6CE8AF18D",1)</f>
-        <v>=DISPIMG("ID_064B3120738647D99CDB63B6CE8AF18D",1)</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="1:3">
-      <c r="A8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="2" t="str">
-        <f>_xlfn.DISPIMG("ID_4941D6FE75C14F29B42CCFDE86C8F2E8",1)</f>
-        <v>=DISPIMG("ID_4941D6FE75C14F29B42CCFDE86C8F2E8",1)</v>
+        <f>_xlfn.DISPIMG("ID_43CB9C70A73E4C3C80385D7854AFA313",1)</f>
+        <v>=DISPIMG("ID_43CB9C70A73E4C3C80385D7854AFA313",1)</v>
       </c>
     </row>
   </sheetData>

--- a/test/kevin-test.xlsx
+++ b/test/kevin-test.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12960"/>
+    <workbookView windowHeight="16560"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
   <etc:cellImage>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="17" name="ID_43CB9C70A73E4C3C80385D7854AFA313"/>
+        <xdr:cNvPr id="34" name="ID_20A60222C7024C7D82AA1EE7E852E745"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -44,124 +44,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4761865" y="3784600"/>
-          <a:ext cx="4248150" cy="7515225"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="15" name="ID_D6D0FC3305F44C7FB61802EAE81D71DB"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4761865" y="2032000"/>
-          <a:ext cx="4381500" cy="7162800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="ID_FE51128C7808427FAE3DB40A613386FE"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4761865" y="1155700"/>
-          <a:ext cx="3971925" cy="6362700"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="16" name="ID_F2475BDC7B71434AAF47DCEFCA0B3D43"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4761865" y="2908300"/>
-          <a:ext cx="3971925" cy="7448550"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="ID_5FE0ED88047D478A9F42F972027B315A"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4761865" y="279400"/>
-          <a:ext cx="4181475" cy="7267575"/>
+          <a:off x="5569585" y="2019300"/>
+          <a:ext cx="13630275" cy="7772400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -177,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>路径</t>
   </si>
@@ -194,34 +78,20 @@
     <t>处理状态</t>
   </si>
   <si>
-    <t>mp-底部tab</t>
+    <t>1. 优惠券不用每次都手动发放，如果是筛选条件，应该自动发放；比如筛选条件是某个时间段新注册用户，那么这个时间段新注册的用户，应该都自动获得优惠券，而不需要手动发放</t>
   </si>
   <si>
-    <t>底部tab的样式不对</t>
+    <t>1. 希望能提前核销，比如用户定了2-3点，到2点半时他又定了一个小时3-4点，那么我们就可以提前给他核销，这里在admin里需要显示一个不一样的样式，如果是同一个用户的相连的时间段，店员能快速发现并提前核销</t>
   </si>
   <si>
-    <t>mp-选择门店</t>
+    <t>1. 可以手动给用户延时，但是这里应该输入分钟，更好记录；
+小程序端如果当前小时时间段有占用，就不可预定；</t>
   </si>
   <si>
-    <t>点击选择门店时，弹出的列表应该是悬浮的，如果不好做，就做成底部弹框吧；目前的向下推压的效果不好</t>
+    <t>1. 有的用户在现场没有手机，希望能在admin里直接实现预定功能将位置锁定给用户</t>
   </si>
   <si>
-    <t>mp-拼豆</t>
-  </si>
-  <si>
-    <t>样式和间距调整一下：1. 标题和上面的间距；2. 到店须知的内间距；3. 选时段一排三个</t>
-  </si>
-  <si>
-    <t>mp-回收</t>
-  </si>
-  <si>
-    <t>页面样式调整：1. 通知的内边距；2. 标题的间距；3. 填写回收物品后的内边距；4. 预计回收时间用户不用操作，我觉得放在编辑回收物品里一起显示；5. 如果当天的选择到店时间已经有人约了，则要变灰</t>
-  </si>
-  <si>
-    <t>mp-我的</t>
-  </si>
-  <si>
-    <t>1. 不需要收藏；2. 我的订单，我的图鉴都去掉，我开过的叫做扭蛋记录；3. 样式调整一下，现在卡片内都没有边距，</t>
+    <t>1. 如果店员一不小心核销了，但是指定错了座位，希望能重新指定座位，应该怎么去做呢</t>
   </si>
 </sst>
 </file>
@@ -850,16 +720,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -867,9 +734,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1400,18 +1264,18 @@
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="69" customHeight="1" outlineLevelRow="5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="18.875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="39.7109375" style="4" customWidth="1"/>
-    <col min="3" max="3" width="40.7578125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="22.3984375" style="3" customWidth="1"/>
-    <col min="5" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="28.8125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="39.7109375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="40.7578125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="22.3984375" style="2" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="22" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -1424,64 +1288,33 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" s="2" customFormat="1" customHeight="1" spans="1:3">
-      <c r="A2" s="2" t="s">
+    <row r="2" ht="68" spans="2:2">
+      <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="6" t="s">
+    </row>
+    <row r="3" customHeight="1" spans="2:2">
+      <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="str">
-        <f>_xlfn.DISPIMG("ID_5FE0ED88047D478A9F42F972027B315A",1)</f>
-        <v>=DISPIMG("ID_5FE0ED88047D478A9F42F972027B315A",1)</v>
+    </row>
+    <row r="4" customHeight="1" spans="2:3">
+      <c r="B4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_20A60222C7024C7D82AA1EE7E852E745",1)</f>
+        <v>=DISPIMG("ID_20A60222C7024C7D82AA1EE7E852E745",1)</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" customHeight="1" spans="1:3">
-      <c r="A3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="6" t="s">
+    <row r="5" customHeight="1" spans="2:2">
+      <c r="B5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="2" t="str">
-        <f>_xlfn.DISPIMG("ID_FE51128C7808427FAE3DB40A613386FE",1)</f>
-        <v>=DISPIMG("ID_FE51128C7808427FAE3DB40A613386FE",1)</v>
-      </c>
     </row>
-    <row r="4" s="2" customFormat="1" customHeight="1" spans="1:3">
-      <c r="A4" s="2" t="s">
+    <row r="6" customHeight="1" spans="2:2">
+      <c r="B6" s="3" t="s">
         <v>9</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="2" t="str">
-        <f>_xlfn.DISPIMG("ID_D6D0FC3305F44C7FB61802EAE81D71DB",1)</f>
-        <v>=DISPIMG("ID_D6D0FC3305F44C7FB61802EAE81D71DB",1)</v>
-      </c>
-    </row>
-    <row r="5" s="2" customFormat="1" customHeight="1" spans="1:3">
-      <c r="A5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="2" t="str">
-        <f>_xlfn.DISPIMG("ID_F2475BDC7B71434AAF47DCEFCA0B3D43",1)</f>
-        <v>=DISPIMG("ID_F2475BDC7B71434AAF47DCEFCA0B3D43",1)</v>
-      </c>
-    </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="1:3">
-      <c r="A6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="2" t="str">
-        <f>_xlfn.DISPIMG("ID_43CB9C70A73E4C3C80385D7854AFA313",1)</f>
-        <v>=DISPIMG("ID_43CB9C70A73E4C3C80385D7854AFA313",1)</v>
       </c>
     </row>
   </sheetData>

--- a/test/kevin-test.xlsx
+++ b/test/kevin-test.xlsx
@@ -31,7 +31,7 @@
   <etc:cellImage>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="34" name="ID_20A60222C7024C7D82AA1EE7E852E745"/>
+        <xdr:cNvPr id="36" name="ID_8707913A477E487A8010081FDD08BDCF"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -44,8 +44,95 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5569585" y="2019300"/>
-          <a:ext cx="13630275" cy="7772400"/>
+          <a:off x="5569585" y="279400"/>
+          <a:ext cx="4581525" cy="8972550"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="37" name="ID_6CD9AC1908A346B2BBDA541B7A2449E2"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5569585" y="1155700"/>
+          <a:ext cx="5162550" cy="8181975"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="38" name="ID_58F11A14F6C34CEAA41C57CC1007464C"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5569585" y="2908300"/>
+          <a:ext cx="4210050" cy="7791450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="39" name="ID_848924F390B74DFD95F091830ACED144"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5569585" y="3784600"/>
+          <a:ext cx="4667250" cy="7820025"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -61,7 +148,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>路径</t>
   </si>
@@ -78,20 +165,41 @@
     <t>处理状态</t>
   </si>
   <si>
-    <t>1. 优惠券不用每次都手动发放，如果是筛选条件，应该自动发放；比如筛选条件是某个时间段新注册用户，那么这个时间段新注册的用户，应该都自动获得优惠券，而不需要手动发放</t>
+    <t>回收-回收预订详情</t>
   </si>
   <si>
-    <t>1. 希望能提前核销，比如用户定了2-3点，到2点半时他又定了一个小时3-4点，那么我们就可以提前给他核销，这里在admin里需要显示一个不一样的样式，如果是同一个用户的相连的时间段，店员能快速发现并提前核销</t>
+    <t>1. 去掉顶部的goods universe / 回收详情
+2. rcy-... 去掉，预约信息里有，submitted也去掉
+3. 回收物品板块去掉，只将点数放到预约信息里
+4. 我拍的实物照也去掉，现在不用拍照</t>
   </si>
   <si>
-    <t>1. 可以手动给用户延时，但是这里应该输入分钟，更好记录；
-小程序端如果当前小时时间段有占用，就不可预定；</t>
+    <t>我的-回收核对</t>
   </si>
   <si>
-    <t>1. 有的用户在现场没有手机，希望能在admin里直接实现预定功能将位置锁定给用户</t>
+    <t>1. 去掉顶部区域和标题；
+2. 日期两个字去掉，日期可以左右滑动，不要顶到右边屏幕外；
+3. 卡片样式适当调整，添加边距，调整样式</t>
   </si>
   <si>
-    <t>1. 如果店员一不小心核销了，但是指定错了座位，希望能重新指定座位，应该怎么去做呢</t>
+    <t>通用</t>
+  </si>
+  <si>
+    <t>所有有goods universe的地方，都去掉</t>
+  </si>
+  <si>
+    <t>我的-回收记录</t>
+  </si>
+  <si>
+    <t>1. 调整卡片样式
+2. 调整列表样式</t>
+  </si>
+  <si>
+    <t>我的-回收核对-详情</t>
+  </si>
+  <si>
+    <t>1. 调整样式
+2. 去掉无用的部分，如用户实物照</t>
   </si>
 </sst>
 </file>
@@ -1288,33 +1396,60 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="68" spans="2:2">
+    <row r="2" customHeight="1" spans="1:3">
+      <c r="A2" s="2" t="s">
+        <v>5</v>
+      </c>
       <c r="B2" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="C2" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_8707913A477E487A8010081FDD08BDCF",1)</f>
+        <v>=DISPIMG("ID_8707913A477E487A8010081FDD08BDCF",1)</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="2:2">
+    <row r="3" customHeight="1" spans="1:3">
+      <c r="A3" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="B3" s="3" t="s">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_6CD9AC1908A346B2BBDA541B7A2449E2",1)</f>
+        <v>=DISPIMG("ID_6CD9AC1908A346B2BBDA541B7A2449E2",1)</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="2:3">
+    <row r="4" customHeight="1" spans="1:2">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="B4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="str">
-        <f>_xlfn.DISPIMG("ID_20A60222C7024C7D82AA1EE7E852E745",1)</f>
-        <v>=DISPIMG("ID_20A60222C7024C7D82AA1EE7E852E745",1)</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="2:2">
+    <row r="5" customHeight="1" spans="1:3">
+      <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="B5" s="3" t="s">
-        <v>8</v>
+        <v>12</v>
+      </c>
+      <c r="C5" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_58F11A14F6C34CEAA41C57CC1007464C",1)</f>
+        <v>=DISPIMG("ID_58F11A14F6C34CEAA41C57CC1007464C",1)</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="2:2">
+    <row r="6" customHeight="1" spans="1:3">
+      <c r="A6" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="B6" s="3" t="s">
-        <v>9</v>
+        <v>14</v>
+      </c>
+      <c r="C6" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_848924F390B74DFD95F091830ACED144",1)</f>
+        <v>=DISPIMG("ID_848924F390B74DFD95F091830ACED144",1)</v>
       </c>
     </row>
   </sheetData>

--- a/test/kevin-test.xlsx
+++ b/test/kevin-test.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16560"/>
+    <workbookView windowWidth="28800" windowHeight="12960"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
   <etc:cellImage>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="36" name="ID_8707913A477E487A8010081FDD08BDCF"/>
+        <xdr:cNvPr id="2" name="ID_8FC929FB98F94E62870BD00F98140E9B"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -45,7 +45,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="5569585" y="279400"/>
-          <a:ext cx="4581525" cy="8972550"/>
+          <a:ext cx="18097500" cy="6705600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -60,7 +60,7 @@
   <etc:cellImage>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="37" name="ID_6CD9AC1908A346B2BBDA541B7A2449E2"/>
+        <xdr:cNvPr id="3" name="ID_A8D45DEE4EE54911B1E4325793C7A77E"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -73,8 +73,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5569585" y="1155700"/>
-          <a:ext cx="5162550" cy="8181975"/>
+          <a:off x="8882380" y="279400"/>
+          <a:ext cx="17907000" cy="8391525"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -89,7 +89,7 @@
   <etc:cellImage>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="38" name="ID_58F11A14F6C34CEAA41C57CC1007464C"/>
+        <xdr:cNvPr id="4" name="ID_3E5F27441F794E1B98EEACD5945717A2"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -102,8 +102,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5569585" y="2908300"/>
-          <a:ext cx="4210050" cy="7791450"/>
+          <a:off x="5569585" y="1917700"/>
+          <a:ext cx="17087850" cy="8162925"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -118,7 +118,7 @@
   <etc:cellImage>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="39" name="ID_848924F390B74DFD95F091830ACED144"/>
+        <xdr:cNvPr id="6" name="ID_A463491F47E047498D6D2862E59EE0C9"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -131,8 +131,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5569585" y="3784600"/>
-          <a:ext cx="4667250" cy="7820025"/>
+          <a:off x="5569585" y="2794000"/>
+          <a:ext cx="18154650" cy="7334250"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -148,7 +148,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>路径</t>
   </si>
@@ -165,41 +165,13 @@
     <t>处理状态</t>
   </si>
   <si>
-    <t>回收-回收预订详情</t>
+    <t>1. admin里不要临时桌，现在的逻辑做的有点复杂，店员很难操作；我们梳理一下，店员创建桌子后，可对桌子或者座位进行开关操作，如果关闭，则小程序上不可预订，但是无论是否关闭，看板功能都不应该受影响。这里的启用功能可以去掉，改成上述描述的开关</t>
   </si>
   <si>
-    <t>1. 去掉顶部的goods universe / 回收详情
-2. rcy-... 去掉，预约信息里有，submitted也去掉
-3. 回收物品板块去掉，只将点数放到预约信息里
-4. 我拍的实物照也去掉，现在不用拍照</t>
+    <t>1. admin里的所有抽屉或者弹框，点击蒙层就应该能自动关闭</t>
   </si>
   <si>
-    <t>我的-回收核对</t>
-  </si>
-  <si>
-    <t>1. 去掉顶部区域和标题；
-2. 日期两个字去掉，日期可以左右滑动，不要顶到右边屏幕外；
-3. 卡片样式适当调整，添加边距，调整样式</t>
-  </si>
-  <si>
-    <t>通用</t>
-  </si>
-  <si>
-    <t>所有有goods universe的地方，都去掉</t>
-  </si>
-  <si>
-    <t>我的-回收记录</t>
-  </si>
-  <si>
-    <t>1. 调整卡片样式
-2. 调整列表样式</t>
-  </si>
-  <si>
-    <t>我的-回收核对-详情</t>
-  </si>
-  <si>
-    <t>1. 调整样式
-2. 去掉无用的部分，如用户实物照</t>
+    <t>1. 红框区域，添加一个板块，动态显示小程序看板日期里没有被预订的座位，同时加一个按钮，可以动态让该座位不在小程序上预订</t>
   </si>
 </sst>
 </file>
@@ -1369,8 +1341,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="69" customHeight="1" outlineLevelRow="5" outlineLevelCol="4"/>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="69" customHeight="1" outlineLevelRow="3" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="28.8125" style="2" customWidth="1"/>
     <col min="2" max="2" width="39.7109375" style="3" customWidth="1"/>
@@ -1396,60 +1368,50 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="1:3">
-      <c r="A2" s="2" t="s">
+    <row r="2" ht="129" customHeight="1" spans="2:4">
+      <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_8FC929FB98F94E62870BD00F98140E9B",1)</f>
+        <v>=DISPIMG("ID_8FC929FB98F94E62870BD00F98140E9B",1)</v>
+      </c>
+      <c r="D2" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_A8D45DEE4EE54911B1E4325793C7A77E",1)</f>
+        <v>=DISPIMG("ID_A8D45DEE4EE54911B1E4325793C7A77E",1)</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已修复(09-26)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="2:3">
+      <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="str">
-        <f>_xlfn.DISPIMG("ID_8707913A477E487A8010081FDD08BDCF",1)</f>
-        <v>=DISPIMG("ID_8707913A477E487A8010081FDD08BDCF",1)</v>
+      <c r="C3" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_3E5F27441F794E1B98EEACD5945717A2",1)</f>
+        <v>=DISPIMG("ID_3E5F27441F794E1B98EEACD5945717A2",1)</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已修复(09-26)</t>
+        </is>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="1:3">
-      <c r="A3" s="2" t="s">
+    <row r="4" customHeight="1" spans="2:3">
+      <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>8</v>
+      <c r="C4" s="2" t="str">
+        <f>_xlfn.DISPIMG("ID_A463491F47E047498D6D2862E59EE0C9",1)</f>
+        <v>=DISPIMG("ID_A463491F47E047498D6D2862E59EE0C9",1)</v>
       </c>
-      <c r="C3" s="2" t="str">
-        <f>_xlfn.DISPIMG("ID_6CD9AC1908A346B2BBDA541B7A2449E2",1)</f>
-        <v>=DISPIMG("ID_6CD9AC1908A346B2BBDA541B7A2449E2",1)</v>
-      </c>
-    </row>
-    <row r="4" customHeight="1" spans="1:2">
-      <c r="A4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" customHeight="1" spans="1:3">
-      <c r="A5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="2" t="str">
-        <f>_xlfn.DISPIMG("ID_58F11A14F6C34CEAA41C57CC1007464C",1)</f>
-        <v>=DISPIMG("ID_58F11A14F6C34CEAA41C57CC1007464C",1)</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="1:3">
-      <c r="A6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="2" t="str">
-        <f>_xlfn.DISPIMG("ID_848924F390B74DFD95F091830ACED144",1)</f>
-        <v>=DISPIMG("ID_848924F390B74DFD95F091830ACED144",1)</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已修复(09-26)</t>
+        </is>
       </c>
     </row>
   </sheetData>
